--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486342_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486342_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.2301</v>
+        <v>11.4325</v>
       </c>
       <c r="E2" t="n">
-        <v>8.291</v>
+        <v>8.092700000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.939</v>
+        <v>3.3397</v>
       </c>
       <c r="G2" t="n">
         <v>6.1259</v>
@@ -610,13 +610,13 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2347</v>
+        <v>0.4371</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5564</v>
+        <v>-0.7547</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7911</v>
+        <v>1.1918</v>
       </c>
       <c r="V2" t="n">
         <v>3.5645</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2647</v>
+        <v>5.1252</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5967</v>
+        <v>1.8887</v>
       </c>
       <c r="F3" t="n">
-        <v>3.668</v>
+        <v>3.2365</v>
       </c>
       <c r="G3" t="n">
         <v>1.7475</v>
@@ -688,13 +688,13 @@
         <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8647</v>
+        <v>0.7252</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8904</v>
+        <v>-0.5984</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7552</v>
+        <v>1.3237</v>
       </c>
       <c r="V3" t="n">
         <v>1.13</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. JOU COLL</t>
+          <t>D. RADONCIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.562</v>
+        <v>2.6006</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9316</v>
+        <v>1.1473</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6304</v>
+        <v>1.4533</v>
       </c>
       <c r="G4" t="n">
-        <v>0.537</v>
+        <v>4.3142</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5959</v>
+        <v>2.1898</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0589</v>
+        <v>2.1244</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1826</v>
+        <v>3.7414</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7331</v>
+        <v>2.9381</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5506</v>
+        <v>0.8032</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3544</v>
+        <v>0.5728</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1372</v>
+        <v>-0.7484</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4916</v>
+        <v>1.3212</v>
       </c>
       <c r="P4" t="n">
-        <v>0.87</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R4" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>3.5248</v>
+        <v>0.6567</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4238</v>
+        <v>-0.4614</v>
       </c>
       <c r="U4" t="n">
-        <v>1.101</v>
+        <v>1.1182</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3698</v>
+        <v>-0.1952</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3252</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.695</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. RADONCIC</t>
+          <t>G. JOU COLL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3154</v>
+        <v>2.5255</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9238</v>
+        <v>1.8334</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3916</v>
+        <v>0.6921</v>
       </c>
       <c r="G5" t="n">
-        <v>4.3142</v>
+        <v>0.537</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1898</v>
+        <v>0.5959</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1244</v>
+        <v>-0.0589</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7414</v>
+        <v>0.1826</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9381</v>
+        <v>0.7331</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8032</v>
+        <v>-0.5506</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5728</v>
+        <v>0.3544</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7484</v>
+        <v>-0.1372</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3212</v>
+        <v>0.4916</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.1751</v>
+        <v>0.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3716</v>
+        <v>1.4883</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.3257</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0565</v>
+        <v>1.1626</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1952</v>
+        <v>-0.3698</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.3252</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.3252</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2439</v>
+        <v>0.8155</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6933</v>
+        <v>-0.1525</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9372</v>
+        <v>0.968</v>
       </c>
       <c r="G6" t="n">
         <v>0.2114</v>
@@ -922,13 +922,13 @@
         <v>0.435</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4024</v>
+        <v>0.1691</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9589</v>
+        <v>-0.4182</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5565</v>
+        <v>0.5873</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1104</v>
+        <v>0.7887</v>
       </c>
       <c r="E7" t="n">
-        <v>0.878</v>
+        <v>1.5305</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9883</v>
+        <v>-0.7418</v>
       </c>
       <c r="G7" t="n">
         <v>2.4966</v>
@@ -1000,13 +1000,13 @@
         <v>0.435</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1046</v>
+        <v>-0.2055</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2329</v>
+        <v>-0.5804</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1283</v>
+        <v>0.3749</v>
       </c>
       <c r="V7" t="n">
         <v>1.3252</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2896</v>
+        <v>-1.0785</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2375</v>
+        <v>-0.0572</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0521</v>
+        <v>-1.0213</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6798999999999999</v>
@@ -1078,13 +1078,13 @@
         <v>0.2175</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.632</v>
+        <v>-0.4209</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.274</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.358</v>
+        <v>-0.3272</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1952</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7837</v>
+        <v>-3.3009</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.9548</v>
+        <v>-3.358</v>
       </c>
       <c r="F9" t="n">
-        <v>0.171</v>
+        <v>0.0571</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1108</v>
+        <v>-1.9139</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.7371</v>
+        <v>-1.3322</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6263</v>
+        <v>-0.5817</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.172</v>
+        <v>-2.0372</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.2867</v>
+        <v>-0.8149</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1147</v>
+        <v>-1.2224</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0612</v>
+        <v>0.1233</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4504</v>
+        <v>-0.5173</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.6407</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R9" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3047</v>
+        <v>0.4602</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8904</v>
+        <v>-0.6237</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1952</v>
+        <v>1.0839</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.3252</v>
+        <v>-2.0647</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1952</v>
+        <v>0.3904</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5204</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0197</v>
+        <v>-3.743</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8303</v>
+        <v>-3.4825</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1895</v>
+        <v>-0.2605</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9139</v>
+        <v>-2.1108</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3322</v>
+        <v>-2.7371</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5817</v>
+        <v>0.6263</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0372</v>
+        <v>-2.172</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8149</v>
+        <v>-2.2867</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2224</v>
+        <v>0.1147</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1233</v>
+        <v>0.0612</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5173</v>
+        <v>-0.4504</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6407</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2175</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2586</v>
+        <v>0.3455</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0959</v>
+        <v>-0.4182</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8373</v>
+        <v>0.7637</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0647</v>
+        <v>-1.3252</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3904</v>
+        <v>0.1952</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.4552</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.5432</v>
+        <v>-6.9262</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.0141</v>
+        <v>-6.1814</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5291</v>
+        <v>-0.7448</v>
       </c>
       <c r="G11" t="n">
         <v>-4.9828</v>
@@ -1312,13 +1312,13 @@
         <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3854</v>
+        <v>0.2316</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3014</v>
+        <v>-0.4687</v>
       </c>
       <c r="U11" t="n">
-        <v>0.916</v>
+        <v>0.7003</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.869500000000001</v>
+        <v>8.2394</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1088999999999993</v>
+        <v>1.260999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>6.9782</v>
+        <v>6.9783</v>
       </c>
       <c r="G12" t="n">
         <v>5.7452</v>
@@ -1390,13 +1390,13 @@
         <v>8.699999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5175</v>
+        <v>3.887299999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.461500000000001</v>
+        <v>-4.0917</v>
       </c>
       <c r="U12" t="n">
-        <v>7.9791</v>
+        <v>7.979200000000001</v>
       </c>
       <c r="V12" t="n">
         <v>1.869599999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.0274</v>
+        <v>5.3531</v>
       </c>
       <c r="E13" t="n">
-        <v>4.8003</v>
+        <v>4.465</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2272</v>
+        <v>0.8881</v>
       </c>
       <c r="G13" t="n">
         <v>1.9692</v>
@@ -1468,13 +1468,13 @@
         <v>1.305</v>
       </c>
       <c r="S13" t="n">
-        <v>0.906</v>
+        <v>0.2316</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0769</v>
+        <v>-0.4122</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9829</v>
+        <v>0.6438</v>
       </c>
       <c r="V13" t="n">
         <v>2.0647</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0687</v>
+        <v>1.9569</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2538</v>
+        <v>0.142</v>
       </c>
       <c r="F14" t="n">
         <v>1.8149</v>
@@ -1546,10 +1546,10 @@
         <v>2.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>0.721</v>
+        <v>0.6093</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5564</v>
+        <v>-0.6681</v>
       </c>
       <c r="U14" t="n">
         <v>1.2774</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. VRANKIC</t>
+          <t>T. BORG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.388</v>
+        <v>0.8978</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6835</v>
+        <v>-0.4396</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2954</v>
+        <v>1.3374</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3557</v>
+        <v>-0.3225</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0372</v>
+        <v>0.4408</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3929</v>
+        <v>-0.7634</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7194</v>
+        <v>0.7016</v>
       </c>
       <c r="K15" t="n">
-        <v>1.521</v>
+        <v>1.4052</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.8016</v>
+        <v>-0.7036</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0751</v>
+        <v>-1.0241</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4838</v>
+        <v>-0.9643</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5913</v>
+        <v>-0.0598</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7401</v>
+        <v>0.6525</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7401</v>
+        <v>1.9576</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0514</v>
+        <v>-0.4491</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5564</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6078</v>
+        <v>0.517</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0477</v>
+        <v>1.017</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5204</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.5682</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. BORG</t>
+          <t>J. VRANKIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2235</v>
+        <v>0.4111</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7749</v>
+        <v>1.4599</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9984</v>
+        <v>-1.0489</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3225</v>
+        <v>-0.3557</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4408</v>
+        <v>1.0372</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7634</v>
+        <v>-1.3929</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7016</v>
+        <v>0.7194</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4052</v>
+        <v>1.521</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7036</v>
+        <v>-0.8016</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0241</v>
+        <v>-1.0751</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9643</v>
+        <v>-0.4838</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0598</v>
+        <v>-0.5913</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6525</v>
+        <v>1.7401</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9576</v>
+        <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1235</v>
+        <v>0.0745</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3014</v>
+        <v>-0.7799</v>
       </c>
       <c r="U16" t="n">
-        <v>0.178</v>
+        <v>0.8544</v>
       </c>
       <c r="V16" t="n">
-        <v>1.017</v>
+        <v>-1.0477</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>1.5204</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.113</v>
+        <v>-2.5682</v>
       </c>
     </row>
     <row r="17">
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1511</v>
+        <v>-0.0393</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1633</v>
+        <v>-0.0515</v>
       </c>
       <c r="F17" t="n">
         <v>0.0122</v>
@@ -1780,10 +1780,10 @@
         <v>1.0875</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.007</v>
+        <v>-0.8953</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1644</v>
+        <v>-1.0527</v>
       </c>
       <c r="U17" t="n">
         <v>0.1574</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2524</v>
+        <v>-0.2447</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9907</v>
+        <v>-0.7672</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7383</v>
+        <v>0.5225</v>
       </c>
       <c r="G18" t="n">
         <v>0.1309</v>
@@ -1858,13 +1858,13 @@
         <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0941</v>
+        <v>0.1018</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.548</v>
+        <v>-0.3245</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6421</v>
+        <v>0.4263</v>
       </c>
       <c r="V18" t="n">
         <v>-1.13</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3391</v>
+        <v>-0.8477</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7531</v>
+        <v>-1.2002</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4141</v>
+        <v>0.3524</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8717</v>
@@ -1936,13 +1936,13 @@
         <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1199</v>
+        <v>-0.3887</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2139</v>
+        <v>-0.6609</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3338</v>
+        <v>0.2722</v>
       </c>
       <c r="V19" t="n">
         <v>0.1952</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4066</v>
+        <v>-1.3141</v>
       </c>
       <c r="E20" t="n">
         <v>-0.7853</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6213</v>
+        <v>-0.5288</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4427</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2244</v>
+        <v>-0.1319</v>
       </c>
       <c r="T20" t="n">
         <v>-0.137</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.08740000000000001</v>
+        <v>0.0051</v>
       </c>
       <c r="V20" t="n">
         <v>-0.7395</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8394</v>
+        <v>-2.6159</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6421</v>
+        <v>-2.4185</v>
       </c>
       <c r="F21" t="n">
         <v>-0.1973</v>
@@ -2092,10 +2092,10 @@
         <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6405</v>
+        <v>-0.417</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0274</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="U21" t="n">
         <v>0.3869</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1233</v>
+        <v>-4.0847</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.9155</v>
+        <v>-4.692</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7922</v>
+        <v>0.6073</v>
       </c>
       <c r="G22" t="n">
         <v>-3.3323</v>
@@ -2170,13 +2170,13 @@
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5703</v>
+        <v>-0.5317</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.5069</v>
+        <v>-1.2834</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9366</v>
+        <v>0.7516</v>
       </c>
       <c r="V22" t="n">
         <v>-0.8732</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.4653</v>
+        <v>-6.342</v>
       </c>
       <c r="E23" t="n">
         <v>-2.691</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.7743</v>
+        <v>-3.651</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8608</v>
@@ -2248,13 +2248,13 @@
         <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.721</v>
       </c>
       <c r="T23" t="n">
         <v>-0.8904</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0461</v>
+        <v>0.1694</v>
       </c>
       <c r="V23" t="n">
         <v>-3.0202</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.869600000000002</v>
+        <v>-6.869499999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.9783</v>
+        <v>-6.9784</v>
       </c>
       <c r="F24" t="n">
-        <v>0.109</v>
+        <v>0.1088</v>
       </c>
       <c r="G24" t="n">
         <v>-5.745100000000001</v>
@@ -2326,13 +2326,13 @@
         <v>11.9628</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.5176</v>
+        <v>-2.5175</v>
       </c>
       <c r="T24" t="n">
-        <v>-7.979099999999999</v>
+        <v>-7.9792</v>
       </c>
       <c r="U24" t="n">
-        <v>5.461600000000001</v>
+        <v>5.461499999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8695</v>
